--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.24462443525204</v>
+        <v>4.264751470728456</v>
       </c>
       <c r="D2" t="n">
-        <v>25.66946289009961</v>
+        <v>4.171287719641187</v>
       </c>
       <c r="E2" t="n">
-        <v>7.212966626132436</v>
+        <v>1.172107076746521</v>
       </c>
       <c r="F2" t="n">
-        <v>6.737571614246572</v>
+        <v>1.094855387315068</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.54226754188775</v>
+        <v>0.9006184755567593</v>
       </c>
       <c r="D3" t="n">
-        <v>5.142803565115716</v>
+        <v>0.8357055793313038</v>
       </c>
       <c r="E3" t="n">
-        <v>7.212966626132436</v>
+        <v>1.172107076746521</v>
       </c>
       <c r="F3" t="n">
-        <v>6.737571614246572</v>
+        <v>1.094855387315068</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3432061812647</v>
+        <v>1.843271004455514</v>
       </c>
       <c r="D4" t="n">
-        <v>12.40150958841298</v>
+        <v>2.015245308117109</v>
       </c>
       <c r="E4" t="n">
-        <v>7.212966626132436</v>
+        <v>1.172107076746521</v>
       </c>
       <c r="F4" t="n">
-        <v>6.737571614246572</v>
+        <v>1.094855387315068</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.36096361370494</v>
+        <v>3.146156587227052</v>
       </c>
       <c r="D5" t="n">
-        <v>10.93308325912882</v>
+        <v>1.776626029608434</v>
       </c>
       <c r="E5" t="n">
-        <v>7.212966626132436</v>
+        <v>1.172107076746521</v>
       </c>
       <c r="F5" t="n">
-        <v>6.737571614246572</v>
+        <v>1.094855387315068</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.52927085943473</v>
+        <v>1.873506514658144</v>
       </c>
       <c r="D6" t="n">
-        <v>12.28899381543708</v>
+        <v>1.996961495008525</v>
       </c>
       <c r="E6" t="n">
-        <v>7.212966626132436</v>
+        <v>1.172107076746521</v>
       </c>
       <c r="F6" t="n">
-        <v>6.737571614246572</v>
+        <v>1.094855387315068</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
